--- a/Data/Bronze/Syllabus/EnfGeomatica/Sistemas de posicionamiento geodésico.xlsx
+++ b/Data/Bronze/Syllabus/EnfGeomatica/Sistemas de posicionamiento geodésico.xlsx
@@ -2765,13 +2765,29 @@
       <c r="J37" s="45"/>
     </row>
     <row r="38" spans="1:10" s="23" customFormat="1">
-      <c r="A38" s="66"/>
+      <c r="A38" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fundamenta matemática y conceptualmente el posicionamiento satelital GNSS.</t>
+        </is>
+      </c>
       <c r="B38" s="68"/>
-      <c r="C38" s="48"/>
+      <c r="C38" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Comprender</t>
+        </is>
+      </c>
       <c r="D38" s="54"/>
       <c r="E38" s="54"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="63"/>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA01</t>
+        </is>
+      </c>
+      <c r="G38" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Explicar los sistemas y marcos de referencia geodésicos, los sistemas de coordenadas y sus transformaciones, y su papel en el posicionamiento GNSS.</t>
+        </is>
+      </c>
       <c r="H38" s="64"/>
       <c r="I38" s="65"/>
       <c r="J38" s="45"/>
@@ -2779,11 +2795,23 @@
     <row r="39" spans="1:10" s="23" customFormat="1">
       <c r="A39" s="66"/>
       <c r="B39" s="68"/>
-      <c r="C39" s="54"/>
+      <c r="C39" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Comprender</t>
+        </is>
+      </c>
       <c r="D39" s="54"/>
       <c r="E39" s="54"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="63"/>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA02</t>
+        </is>
+      </c>
+      <c r="G39" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Describir la arquitectura de los sistemas GNSS: segmentos, señales, escalas de tiempo y órbitas satelitales.</t>
+        </is>
+      </c>
       <c r="H39" s="64"/>
       <c r="I39" s="65"/>
       <c r="J39" s="45"/>
@@ -2791,11 +2819,23 @@
     <row r="40" spans="1:10" s="23" customFormat="1">
       <c r="A40" s="66"/>
       <c r="B40" s="68"/>
-      <c r="C40" s="54"/>
+      <c r="C40" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Aplicar</t>
+        </is>
+      </c>
       <c r="D40" s="54"/>
       <c r="E40" s="54"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="63"/>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA03</t>
+        </is>
+      </c>
+      <c r="G40" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelar los efectos atmosféricos y de deformación de la Tierra que afectan las mediciones GNSS y aplicar las correcciones correspondientes.</t>
+        </is>
+      </c>
       <c r="H40" s="64"/>
       <c r="I40" s="65"/>
       <c r="J40" s="45"/>
@@ -2803,23 +2843,51 @@
     <row r="41" spans="1:10" s="23" customFormat="1">
       <c r="A41" s="66"/>
       <c r="B41" s="68"/>
-      <c r="C41" s="54"/>
+      <c r="C41" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Aplicar</t>
+        </is>
+      </c>
       <c r="D41" s="54"/>
       <c r="E41" s="54"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="66"/>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA04</t>
+        </is>
+      </c>
+      <c r="G41" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolver las ecuaciones de navegación mediante ajuste de parámetros y filtro de Kalman, y estimar el error de posicionamiento.</t>
+        </is>
+      </c>
       <c r="H41" s="67"/>
       <c r="I41" s="68"/>
       <c r="J41" s="45"/>
     </row>
     <row r="42" spans="1:10" s="23" customFormat="1">
-      <c r="A42" s="66"/>
+      <c r="A42" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procesa datos GNSS y desarrolla proyectos aplicados a las ciencias de la Tierra.</t>
+        </is>
+      </c>
       <c r="B42" s="68"/>
-      <c r="C42" s="54"/>
+      <c r="C42" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Analizar</t>
+        </is>
+      </c>
       <c r="D42" s="54"/>
       <c r="E42" s="54"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="69"/>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA05</t>
+        </is>
+      </c>
+      <c r="G42" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procesar datos GNSS con los métodos diferencial, cinemático y de posicionamiento por punto preciso (PPP), conforme a estándares internacionales, y analizar la precisión de las coordenadas obtenidas.</t>
+        </is>
+      </c>
       <c r="H42" s="70"/>
       <c r="I42" s="71"/>
       <c r="J42" s="45"/>
@@ -2827,11 +2895,23 @@
     <row r="43" spans="1:10" s="23" customFormat="1">
       <c r="A43" s="66"/>
       <c r="B43" s="68"/>
-      <c r="C43" s="72"/>
+      <c r="C43" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Crear</t>
+        </is>
+      </c>
       <c r="D43" s="73"/>
       <c r="E43" s="74"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="66"/>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA06</t>
+        </is>
+      </c>
+      <c r="G43" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formular y desarrollar un proyecto de aplicación GNSS en ciencias de la Tierra (geodinámica, geofísica, oceanografía o meteorología).</t>
+        </is>
+      </c>
       <c r="H43" s="67"/>
       <c r="I43" s="68"/>
       <c r="J43" s="14"/>
@@ -3077,8 +3157,16 @@
       <c r="B60" s="81"/>
       <c r="C60" s="81"/>
       <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
+      <c r="E60" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="F60" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G60" s="36"/>
       <c r="H60" s="36"/>
       <c r="I60" s="36"/>
@@ -3091,8 +3179,16 @@
       <c r="B61" s="81"/>
       <c r="C61" s="81"/>
       <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="36"/>
+      <c r="E61" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="F61" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G61" s="36"/>
       <c r="H61" s="37"/>
       <c r="I61" s="36"/>
@@ -3105,7 +3201,11 @@
       <c r="B62" s="81"/>
       <c r="C62" s="81"/>
       <c r="D62" s="36"/>
-      <c r="E62" s="36"/>
+      <c r="E62" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="F62" s="36"/>
       <c r="G62" s="36"/>
       <c r="H62" s="36"/>
@@ -3119,8 +3219,16 @@
       <c r="B63" s="81"/>
       <c r="C63" s="81"/>
       <c r="D63" s="36"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="36"/>
+      <c r="E63" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="F63" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G63" s="36"/>
       <c r="H63" s="36"/>
       <c r="I63" s="36"/>
@@ -3133,10 +3241,18 @@
       <c r="B64" s="81"/>
       <c r="C64" s="81"/>
       <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
+      <c r="E64" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="F64" s="36"/>
       <c r="G64" s="36"/>
-      <c r="H64" s="37"/>
+      <c r="H64" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="I64" s="36"/>
       <c r="J64" s="84"/>
     </row>
@@ -3150,8 +3266,16 @@
       <c r="E65" s="37"/>
       <c r="F65" s="36"/>
       <c r="G65" s="36"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="36"/>
+      <c r="H65" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="I65" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="J65" s="84"/>
     </row>
     <row r="66" spans="1:10">
@@ -3203,11 +3327,27 @@
       <c r="B69" s="81"/>
       <c r="C69" s="81"/>
       <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
+      <c r="E69" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHP</t>
+        </is>
+      </c>
+      <c r="F69" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EE</t>
+        </is>
+      </c>
       <c r="G69" s="37"/>
-      <c r="H69" s="37"/>
-      <c r="I69" s="37"/>
+      <c r="H69" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EBP</t>
+        </is>
+      </c>
+      <c r="I69" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EOP</t>
+        </is>
+      </c>
       <c r="J69" s="84"/>
     </row>
     <row r="70" spans="1:10">
@@ -3217,11 +3357,27 @@
       <c r="B70" s="81"/>
       <c r="C70" s="81"/>
       <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
+      <c r="E70" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30%</t>
+        </is>
+      </c>
+      <c r="F70" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25%</t>
+        </is>
+      </c>
       <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
+      <c r="H70" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30%</t>
+        </is>
+      </c>
+      <c r="I70" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15%</t>
+        </is>
+      </c>
       <c r="J70" s="84"/>
     </row>
     <row r="71" spans="1:10">
@@ -3231,11 +3387,27 @@
       <c r="B71" s="81"/>
       <c r="C71" s="81"/>
       <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
       <c r="G71" s="16"/>
-      <c r="H71" s="16"/>
-      <c r="I71" s="16"/>
+      <c r="H71" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
       <c r="J71" s="84"/>
     </row>
     <row r="72" spans="1:10">
